--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\PITPM_1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376154FC-543A-44B2-AA97-DBE3CEE92921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="45" windowWidth="27795" windowHeight="12600"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>UIDTC</t>
   </si>
@@ -34,16 +40,103 @@
   </si>
   <si>
     <t>Фактический результат</t>
+  </si>
+  <si>
+    <t>CP_TC_1</t>
+  </si>
+  <si>
+    <t>CP_TC_2</t>
+  </si>
+  <si>
+    <t>Построение арифметической прогрессии</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Построен отрезок с началом в точке (1;0) и концом в точке (5;8)</t>
+  </si>
+  <si>
+    <t>Построение геометрической прогрессии</t>
+  </si>
+  <si>
+    <t>Построена ломаная с началом в точке (1;1) и концом в точке (5;16)</t>
+  </si>
+  <si>
+    <t>V_TC_1</t>
+  </si>
+  <si>
+    <t>V_TC_2</t>
+  </si>
+  <si>
+    <t>V_TC_3</t>
+  </si>
+  <si>
+    <t>Валидация пустых полей ввода</t>
+  </si>
+  <si>
+    <t>1) Нажать на "Создать"</t>
+  </si>
+  <si>
+    <t>1) В поле "Начальное значение" ввести 1
+2) В поле "Шаг" ввести 2
+3) В поле "Количество точек" ввести значение 5
+4) В поле "Тип прогрессии" выбрать "Геометрическая"
+5) Нажать на "Создать"</t>
+  </si>
+  <si>
+    <t>1) В поле "Начальное значение" ввести 0
+2) В поле "Шаг" ввести 2
+3) В поле "Количество точек" ввести значение 5
+4) В поле "Тип прогрессии" выбрать "Арифметическая"
+5) Нажать на "Создать"</t>
+  </si>
+  <si>
+    <t>Хотя бы одно из текстовых полей пусто</t>
+  </si>
+  <si>
+    <t>Показано окно "Предупреждение" с текстом "Заполните все текстовые поля"</t>
+  </si>
+  <si>
+    <t>Валидация некорректных числовых значений</t>
+  </si>
+  <si>
+    <t>1) Текстовые поля не пусты
+2) Хотя бы в одно из текстовых полей введено нечисловое значение</t>
+  </si>
+  <si>
+    <t>Показано окно "Предупреждение" с текстом "Укажите корректные значения"</t>
+  </si>
+  <si>
+    <t>Программа завершила свою работу с исключением FormatException</t>
+  </si>
+  <si>
+    <t>Проверка выбора типа прогрессии</t>
+  </si>
+  <si>
+    <t>1) Текстовые поля не пусты
+2) Во все текстовые поля введены корректные числовые значения
+3) Тип прогрессии не выбран</t>
+  </si>
+  <si>
+    <t>Показано окно "Предупреждение" с текстом "Выберите тип прогрессии"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -85,30 +178,109 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF99FF99"/>
+      <color rgb="FFFF9999"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -146,7 +318,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -218,7 +390,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -391,16 +563,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="6" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -410,7 +581,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -423,53 +594,122 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+    <row r="2" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+    <row r="3" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+    <row r="4" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+    <row r="5" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+    <row r="6" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:F6">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$F2=$E2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$F2&lt;&gt;$E2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -478,7 +718,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\PITPM_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376154FC-543A-44B2-AA97-DBE3CEE92921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28D612-4A9F-449B-992F-08022CFB04A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>UIDTC</t>
   </si>
@@ -76,20 +76,6 @@
   </si>
   <si>
     <t>1) Нажать на "Создать"</t>
-  </si>
-  <si>
-    <t>1) В поле "Начальное значение" ввести 1
-2) В поле "Шаг" ввести 2
-3) В поле "Количество точек" ввести значение 5
-4) В поле "Тип прогрессии" выбрать "Геометрическая"
-5) Нажать на "Создать"</t>
-  </si>
-  <si>
-    <t>1) В поле "Начальное значение" ввести 0
-2) В поле "Шаг" ввести 2
-3) В поле "Количество точек" ввести значение 5
-4) В поле "Тип прогрессии" выбрать "Арифметическая"
-5) Нажать на "Создать"</t>
   </si>
   <si>
     <t>Хотя бы одно из текстовых полей пусто</t>
@@ -120,6 +106,38 @@
   </si>
   <si>
     <t>Показано окно "Предупреждение" с текстом "Выберите тип прогрессии"</t>
+  </si>
+  <si>
+    <t>Входные данные</t>
+  </si>
+  <si>
+    <t>1) Начальное значение: 0
+2) Шаг: 2
+3) Количество точек: 5</t>
+  </si>
+  <si>
+    <t>1) Ввести входные данные в соответствующие поля
+2) В поле "Тип прогрессии" выбрать "Арифметическая"
+3) Нажать на "Создать"</t>
+  </si>
+  <si>
+    <t>1) Начальное значение: 1
+2) Шаг: 2
+3) Количество точек: 5</t>
+  </si>
+  <si>
+    <t>1) Ввести входные данные в соответствующие поля
+2) В поле "Тип прогрессии" выбрать "Геометрическая"
+3) Нажать на "Создать"</t>
+  </si>
+  <si>
+    <t>1) Начальное значение: abc
+2) Шаг: 2
+3) Количество точек: 5</t>
+  </si>
+  <si>
+    <t>1) Ввести входные данные в соответствующие поля
+2) Нажать на "Создать"</t>
   </si>
 </sst>
 </file>
@@ -208,7 +226,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -220,41 +238,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -564,17 +547,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="6" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="7" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,17 +568,20 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -604,17 +591,20 @@
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>19</v>
+      <c r="D2" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -624,17 +614,20 @@
       <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>18</v>
+      <c r="D3" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -642,65 +635,74 @@
         <v>16</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="6" spans="1:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:F6">
+  <conditionalFormatting sqref="A2:G6">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$G2&lt;&gt;$F2</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$F2=$E2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$F2&lt;&gt;$E2</formula>
+      <formula>$G2=$F2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
